--- a/data/k-props/2026-08-13.xlsx
+++ b/data/k-props/2026-08-13.xlsx
@@ -145,63 +145,63 @@
     <t>2026-08-13</t>
   </si>
   <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago White Sox</t>
+  </si>
+  <si>
     <t>Davis Martin</t>
   </si>
   <si>
-    <t/>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Tyler Phillips</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Max Fried</t>
   </si>
   <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Cincinnati Reds @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Tyler Phillips</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Max Fried</t>
-  </si>
-  <si>
     <t>Payton Tolle</t>
   </si>
   <si>
@@ -214,49 +214,49 @@
     <t>Limited starter</t>
   </si>
   <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Washington Nationals</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Washington Nationals</t>
-  </si>
-  <si>
     <t>Cade Cavalli</t>
   </si>
   <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
     <t>Taj Bradley</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Shane Drohan</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Roki Sasaki</t>
   </si>
   <si>
     <t>Walbert Urena</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>Roki Sasaki</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Shane Drohan</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
   </si>
 </sst>
 </file>
@@ -782,16 +782,16 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D2">
-        <v>-119</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>105</v>
+        <v>-116</v>
       </c>
       <c r="F2">
-        <v>6.01</v>
+        <v>5.29</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -800,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>6.01</v>
+        <v>5.29</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -809,13 +809,13 @@
         <v>47</v>
       </c>
       <c r="N2">
-        <v>824561</v>
+        <v>824238</v>
       </c>
       <c r="O2" t="s">
         <v>48</v>
       </c>
       <c r="P2">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -824,55 +824,55 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>0.2081</v>
+        <v>0.2509</v>
       </c>
       <c r="U2">
-        <v>0.1908</v>
+        <v>0.242</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="X2">
-        <v>0.1569</v>
+        <v>0.2269</v>
       </c>
       <c r="Y2">
-        <v>0.338</v>
+        <v>0.373</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>4.22</v>
+        <v>3.97</v>
       </c>
       <c r="AB2">
-        <v>1.3005</v>
+        <v>0.9501</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2905</v>
+        <v>0.2128</v>
       </c>
       <c r="AE2">
-        <v>0.2857</v>
+        <v>0.2093</v>
       </c>
       <c r="AF2">
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.2564</v>
+        <v>0.226</v>
       </c>
       <c r="AH2">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI2">
-        <v>1.0729</v>
+        <v>0.976</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -895,16 +895,16 @@
         <v>51</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>-105</v>
+        <v>-170</v>
       </c>
       <c r="E3">
-        <v>-110</v>
+        <v>136</v>
       </c>
       <c r="F3">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -913,22 +913,22 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="L3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M3" t="s">
         <v>47</v>
       </c>
       <c r="N3">
-        <v>824561</v>
+        <v>824238</v>
       </c>
       <c r="O3" t="s">
         <v>48</v>
       </c>
       <c r="P3">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -937,55 +937,55 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>0.1784</v>
+        <v>0.1748</v>
       </c>
       <c r="U3">
-        <v>0.1693</v>
+        <v>0.1692</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="X3">
-        <v>0.1538</v>
+        <v>0.1597</v>
       </c>
       <c r="Y3">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.31</v>
+        <v>4.02</v>
       </c>
       <c r="AB3">
-        <v>0.9511</v>
+        <v>0.7366</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.2125</v>
+        <v>0.165</v>
       </c>
       <c r="AE3">
-        <v>0.2282</v>
+        <v>0.1787</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.247</v>
+        <v>0.2159</v>
       </c>
       <c r="AH3">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI3">
-        <v>0.9662</v>
+        <v>0.88</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1005,43 +1005,43 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>-105</v>
+      </c>
+      <c r="E4">
+        <v>-110</v>
+      </c>
+      <c r="F4">
+        <v>3.59</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4">
+        <v>3.59</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
         <v>53</v>
       </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-      <c r="D4">
-        <v>102</v>
-      </c>
-      <c r="E4">
-        <v>-116</v>
-      </c>
-      <c r="F4">
-        <v>5.3</v>
-      </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4">
-        <v>5.3</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" t="s">
-        <v>54</v>
-      </c>
       <c r="N4">
-        <v>824238</v>
+        <v>824561</v>
       </c>
       <c r="O4" t="s">
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1050,55 +1050,55 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>0.2509</v>
+        <v>0.1784</v>
       </c>
       <c r="U4">
-        <v>0.242</v>
+        <v>0.1693</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="X4">
-        <v>0.2269</v>
+        <v>0.1538</v>
       </c>
       <c r="Y4">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="AB4">
-        <v>0.9524</v>
+        <v>0.9488</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
       <c r="AD4">
-        <v>0.2128</v>
+        <v>0.2125</v>
       </c>
       <c r="AE4">
-        <v>0.2093</v>
+        <v>0.2282</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.226</v>
+        <v>0.247</v>
       </c>
       <c r="AH4">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI4">
-        <v>0.976</v>
+        <v>0.9662</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
@@ -1118,19 +1118,19 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-170</v>
+        <v>-119</v>
       </c>
       <c r="E5">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>2.51</v>
+        <v>5.99</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1139,22 +1139,22 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>2.51</v>
+        <v>5.99</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N5">
-        <v>824238</v>
+        <v>824561</v>
       </c>
       <c r="O5" t="s">
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1163,55 +1163,55 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>0.1748</v>
+        <v>0.2081</v>
       </c>
       <c r="U5">
-        <v>0.1692</v>
+        <v>0.1908</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="X5">
-        <v>0.1597</v>
+        <v>0.1569</v>
       </c>
       <c r="Y5">
-        <v>0.373</v>
+        <v>0.338</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.02</v>
+        <v>4.22</v>
       </c>
       <c r="AB5">
-        <v>0.7384</v>
+        <v>1.2973</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.165</v>
+        <v>0.2905</v>
       </c>
       <c r="AE5">
-        <v>0.1787</v>
+        <v>0.2857</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2159</v>
+        <v>0.2564</v>
       </c>
       <c r="AH5">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI5">
-        <v>0.88</v>
+        <v>1.0729</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1231,7 +1231,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>5.5</v>
@@ -1243,7 +1243,7 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1252,13 +1252,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N6">
         <v>823829</v>
@@ -1303,7 +1303,7 @@
         <v>4.13</v>
       </c>
       <c r="AB6">
-        <v>0.9685</v>
+        <v>0.9661</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1321,7 +1321,7 @@
         <v>0.2096</v>
       </c>
       <c r="AH6">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI6">
         <v>0.8828</v>
@@ -1344,7 +1344,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1356,7 +1356,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1365,13 +1365,13 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7">
         <v>823829</v>
@@ -1416,7 +1416,7 @@
         <v>4.3</v>
       </c>
       <c r="AB7">
-        <v>1.1276</v>
+        <v>1.1248</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1434,7 +1434,7 @@
         <v>0.2358</v>
       </c>
       <c r="AH7">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI7">
         <v>1.0657</v>
@@ -1457,7 +1457,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>6.5</v>
@@ -1469,7 +1469,7 @@
         <v>115</v>
       </c>
       <c r="F8">
-        <v>6.61</v>
+        <v>6.59</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1478,13 +1478,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>7.21</v>
+        <v>7.19</v>
       </c>
       <c r="L8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" t="s">
         <v>60</v>
-      </c>
-      <c r="M8" t="s">
-        <v>61</v>
       </c>
       <c r="N8">
         <v>823508</v>
@@ -1529,7 +1529,7 @@
         <v>3.94</v>
       </c>
       <c r="AB8">
-        <v>1.1719</v>
+        <v>1.1691</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>0.2432</v>
       </c>
       <c r="AH8">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI8">
         <v>1.0144</v>
@@ -1570,7 +1570,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1582,7 +1582,7 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1591,13 +1591,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N9">
         <v>823508</v>
@@ -1642,7 +1642,7 @@
         <v>3.84</v>
       </c>
       <c r="AB9">
-        <v>1.0385</v>
+        <v>1.0359</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1660,7 +1660,7 @@
         <v>0.2383</v>
       </c>
       <c r="AH9">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI9">
         <v>1.0083</v>
@@ -1695,7 +1695,7 @@
         <v>103</v>
       </c>
       <c r="F10">
-        <v>6.49</v>
+        <v>6.48</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1704,10 +1704,10 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>6.49</v>
+        <v>6.48</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
@@ -1755,7 +1755,7 @@
         <v>4.07</v>
       </c>
       <c r="AB10">
-        <v>0.9052</v>
+        <v>0.903</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1773,7 +1773,7 @@
         <v>0.2131</v>
       </c>
       <c r="AH10">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI10">
         <v>0.9582</v>
@@ -1808,7 +1808,7 @@
         <v>-158</v>
       </c>
       <c r="F11">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1817,10 +1817,10 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M11" t="s">
         <v>64</v>
@@ -1868,16 +1868,16 @@
         <v>4.47</v>
       </c>
       <c r="AB11">
-        <v>0.852</v>
+        <v>0.8937</v>
       </c>
       <c r="AC11" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.1903</v>
+        <v>0.2001</v>
       </c>
       <c r="AE11">
-        <v>0.189</v>
+        <v>0.1945</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1886,19 +1886,19 @@
         <v>0.2175</v>
       </c>
       <c r="AH11">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI11">
-        <v>0.9795</v>
+        <v>1.0056</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1921,7 +1921,7 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1930,13 +1930,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N12">
         <v>822696</v>
@@ -1981,10 +1981,10 @@
         <v>4.21</v>
       </c>
       <c r="AB12">
-        <v>0.9393</v>
+        <v>0.9371</v>
       </c>
       <c r="AC12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD12">
         <v>0.2099</v>
@@ -1999,7 +1999,7 @@
         <v>0.2058</v>
       </c>
       <c r="AH12">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI12">
         <v>1.0235</v>
@@ -2008,10 +2008,10 @@
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>-140</v>
       </c>
       <c r="F13">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2043,13 +2043,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N13">
         <v>822696</v>
@@ -2094,10 +2094,10 @@
         <v>4.29</v>
       </c>
       <c r="AB13">
-        <v>1.0064</v>
+        <v>1.0039</v>
       </c>
       <c r="AC13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD13">
         <v>0.2248</v>
@@ -2112,7 +2112,7 @@
         <v>0.2169</v>
       </c>
       <c r="AH13">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI13">
         <v>0.9827</v>
@@ -2121,10 +2121,10 @@
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2141,13 +2141,13 @@
         <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-125</v>
+        <v>130</v>
       </c>
       <c r="E14">
-        <v>111</v>
+        <v>-152</v>
       </c>
       <c r="F14">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2156,10 +2156,10 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
         <v>73</v>
@@ -2171,7 +2171,7 @@
         <v>48</v>
       </c>
       <c r="P14">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -2183,61 +2183,61 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>0.2662</v>
+        <v>0.2371</v>
       </c>
       <c r="U14">
-        <v>0.2561</v>
+        <v>0.2333</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="X14">
-        <v>0.24</v>
+        <v>0.2269</v>
       </c>
       <c r="Y14">
-        <v>0.385</v>
+        <v>0.373</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.22</v>
+        <v>4.35</v>
       </c>
       <c r="AB14">
-        <v>0.8212</v>
+        <v>0.8671</v>
       </c>
       <c r="AC14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD14">
-        <v>0.1835</v>
+        <v>0.1942</v>
       </c>
       <c r="AE14">
-        <v>0.1858</v>
+        <v>0.1943</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
       <c r="AG14">
-        <v>0.2264</v>
+        <v>0.2096</v>
       </c>
       <c r="AH14">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI14">
-        <v>0.9744</v>
+        <v>0.9817</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2254,13 +2254,13 @@
         <v>5.5</v>
       </c>
       <c r="D15">
-        <v>130</v>
+        <v>-125</v>
       </c>
       <c r="E15">
-        <v>-152</v>
+        <v>111</v>
       </c>
       <c r="F15">
-        <v>4.51</v>
+        <v>4.94</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2269,10 +2269,10 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.51</v>
+        <v>4.94</v>
       </c>
       <c r="L15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M15" t="s">
         <v>73</v>
@@ -2284,7 +2284,7 @@
         <v>48</v>
       </c>
       <c r="P15">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2296,61 +2296,61 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>0.2371</v>
+        <v>0.2662</v>
       </c>
       <c r="U15">
-        <v>0.2333</v>
+        <v>0.2561</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="X15">
-        <v>0.2269</v>
+        <v>0.24</v>
       </c>
       <c r="Y15">
-        <v>0.373</v>
+        <v>0.385</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="AB15">
-        <v>0.8692</v>
+        <v>0.8192</v>
       </c>
       <c r="AC15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD15">
-        <v>0.1942</v>
+        <v>0.1835</v>
       </c>
       <c r="AE15">
-        <v>0.1943</v>
+        <v>0.1858</v>
       </c>
       <c r="AF15">
         <v>9</v>
       </c>
       <c r="AG15">
-        <v>0.2096</v>
+        <v>0.2264</v>
       </c>
       <c r="AH15">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI15">
-        <v>0.9817</v>
+        <v>0.9744</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2364,13 +2364,16 @@
         <v>75</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16">
-        <v>-142</v>
+        <v>-120</v>
       </c>
       <c r="E16">
-        <v>112</v>
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>7.45</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2378,32 +2381,92 @@
       <c r="J16" t="s">
         <v>45</v>
       </c>
+      <c r="K16">
+        <v>8.05</v>
+      </c>
       <c r="L16" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M16" t="s">
         <v>76</v>
       </c>
-      <c r="N16" t="s">
-        <v>45</v>
+      <c r="N16">
+        <v>823995</v>
       </c>
       <c r="O16" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P16">
+        <v>5.4</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
       </c>
       <c r="S16">
         <v>6</v>
       </c>
+      <c r="T16">
+        <v>0.2963</v>
+      </c>
+      <c r="U16">
+        <v>0.2884</v>
+      </c>
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>106</v>
+      </c>
+      <c r="X16">
+        <v>0.2736</v>
+      </c>
+      <c r="Y16">
+        <v>0.346</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>4.1</v>
+      </c>
+      <c r="AB16">
+        <v>1.2068</v>
+      </c>
       <c r="AC16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>45</v>
+        <v>69</v>
+      </c>
+      <c r="AD16">
+        <v>0.2703</v>
+      </c>
+      <c r="AE16">
+        <v>0.2627</v>
+      </c>
+      <c r="AF16">
+        <v>9</v>
+      </c>
+      <c r="AG16">
+        <v>0.2504</v>
+      </c>
+      <c r="AH16">
+        <v>0.224</v>
+      </c>
+      <c r="AI16">
+        <v>1.0463</v>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AL16" t="s">
-        <v>45</v>
+        <v>70</v>
+      </c>
+      <c r="AM16">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2413,17 +2476,8 @@
       <c r="B17" t="s">
         <v>77</v>
       </c>
-      <c r="C17">
-        <v>6.5</v>
-      </c>
-      <c r="D17">
-        <v>-120</v>
-      </c>
-      <c r="E17">
-        <v>100</v>
-      </c>
       <c r="F17">
-        <v>7.47</v>
+        <v>4.98</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2432,10 +2486,10 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>8.07</v>
+        <v>4.98</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
         <v>76</v>
@@ -2447,7 +2501,7 @@
         <v>48</v>
       </c>
       <c r="P17">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2456,67 +2510,67 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0.2963</v>
+        <v>0.2225</v>
       </c>
       <c r="U17">
-        <v>0.2884</v>
+        <v>0.2224</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="X17">
-        <v>0.2736</v>
+        <v>0.2222</v>
       </c>
       <c r="Y17">
-        <v>0.346</v>
+        <v>0.331</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>4.1</v>
+        <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>1.2098</v>
+        <v>0.9654</v>
       </c>
       <c r="AC17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD17">
-        <v>0.2703</v>
+        <v>0.2162</v>
       </c>
       <c r="AE17">
-        <v>0.2627</v>
+        <v>0.2344</v>
       </c>
       <c r="AF17">
         <v>9</v>
       </c>
       <c r="AG17">
-        <v>0.2504</v>
+        <v>0.2203</v>
       </c>
       <c r="AH17">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI17">
-        <v>1.0463</v>
+        <v>1.0271</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM17">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2527,16 +2581,16 @@
         <v>78</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-124</v>
+        <v>102</v>
       </c>
       <c r="E18">
-        <v>107</v>
+        <v>-120</v>
       </c>
       <c r="F18">
-        <v>5.12</v>
+        <v>6.86</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2545,10 +2599,10 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>5.12</v>
+        <v>6.86</v>
       </c>
       <c r="L18" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
@@ -2572,61 +2626,61 @@
         <v>6</v>
       </c>
       <c r="T18">
-        <v>0.2377</v>
+        <v>0.2385</v>
       </c>
       <c r="U18">
-        <v>0.2477</v>
+        <v>0.2467</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="X18">
-        <v>0.265</v>
+        <v>0.2602</v>
       </c>
       <c r="Y18">
-        <v>0.369</v>
+        <v>0.381</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="AB18">
-        <v>0.9199</v>
+        <v>1.2574</v>
       </c>
       <c r="AC18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD18">
-        <v>0.2055</v>
+        <v>0.2816</v>
       </c>
       <c r="AE18">
-        <v>0.2331</v>
+        <v>0.2193</v>
       </c>
       <c r="AF18">
         <v>9</v>
       </c>
       <c r="AG18">
-        <v>0.2145</v>
+        <v>0.1991</v>
       </c>
       <c r="AH18">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI18">
-        <v>1.0081</v>
+        <v>1.0027</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2640,16 +2694,16 @@
         <v>80</v>
       </c>
       <c r="C19">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D19">
-        <v>102</v>
+        <v>-124</v>
       </c>
       <c r="E19">
-        <v>-120</v>
+        <v>107</v>
       </c>
       <c r="F19">
-        <v>6.87</v>
+        <v>5.11</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2658,7 +2712,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>6.87</v>
+        <v>5.11</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -2685,61 +2739,61 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>0.2385</v>
+        <v>0.2377</v>
       </c>
       <c r="U19">
-        <v>0.2467</v>
+        <v>0.2477</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="X19">
-        <v>0.2602</v>
+        <v>0.265</v>
       </c>
       <c r="Y19">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="AB19">
-        <v>1.2605</v>
+        <v>0.9176</v>
       </c>
       <c r="AC19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD19">
-        <v>0.2816</v>
+        <v>0.2055</v>
       </c>
       <c r="AE19">
-        <v>0.2193</v>
+        <v>0.2331</v>
       </c>
       <c r="AF19">
         <v>9</v>
       </c>
       <c r="AG19">
-        <v>0.1991</v>
+        <v>0.2145</v>
       </c>
       <c r="AH19">
-        <v>0.2234</v>
+        <v>0.224</v>
       </c>
       <c r="AI19">
-        <v>1.0027</v>
+        <v>1.0081</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AL19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2752,8 +2806,14 @@
       <c r="B20" t="s">
         <v>81</v>
       </c>
-      <c r="F20">
-        <v>4.99</v>
+      <c r="C20">
+        <v>4.5</v>
+      </c>
+      <c r="D20">
+        <v>-142</v>
+      </c>
+      <c r="E20">
+        <v>112</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2761,92 +2821,32 @@
       <c r="J20" t="s">
         <v>45</v>
       </c>
-      <c r="K20">
-        <v>4.99</v>
-      </c>
       <c r="L20" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M20" t="s">
         <v>76</v>
       </c>
-      <c r="N20">
-        <v>823995</v>
+      <c r="N20" t="s">
+        <v>45</v>
       </c>
       <c r="O20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P20">
-        <v>5.3</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0.2225</v>
-      </c>
-      <c r="U20">
-        <v>0.2224</v>
-      </c>
-      <c r="V20">
-        <v>5</v>
-      </c>
-      <c r="W20">
-        <v>99</v>
-      </c>
-      <c r="X20">
-        <v>0.2222</v>
-      </c>
-      <c r="Y20">
-        <v>0.331</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>4.29</v>
-      </c>
-      <c r="AB20">
-        <v>0.9677</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD20">
-        <v>0.2162</v>
-      </c>
-      <c r="AE20">
-        <v>0.2344</v>
-      </c>
-      <c r="AF20">
-        <v>9</v>
-      </c>
-      <c r="AG20">
-        <v>0.2203</v>
-      </c>
-      <c r="AH20">
-        <v>0.2234</v>
-      </c>
-      <c r="AI20">
-        <v>1.0271</v>
-      </c>
-      <c r="AJ20" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>45</v>
       </c>
       <c r="AK20" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="AL20" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-13.xlsx
+++ b/data/k-props/2026-08-13.xlsx
@@ -220,19 +220,19 @@
     <t>Chicago Cubs @ Washington Nationals</t>
   </si>
   <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
   </si>
   <si>
     <t>Taj Bradley</t>
@@ -791,7 +791,7 @@
         <v>-116</v>
       </c>
       <c r="F2">
-        <v>5.29</v>
+        <v>5.57</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -800,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>5.29</v>
+        <v>5.57</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -827,22 +827,22 @@
         <v>5</v>
       </c>
       <c r="T2">
-        <v>0.2509</v>
+        <v>0.2513</v>
       </c>
       <c r="U2">
-        <v>0.242</v>
+        <v>0.2571</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="X2">
-        <v>0.2269</v>
+        <v>0.2667</v>
       </c>
       <c r="Y2">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>3.97</v>
       </c>
       <c r="AB2">
-        <v>0.9501</v>
+        <v>0.9428</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -866,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.226</v>
+        <v>0.2257</v>
       </c>
       <c r="AH2">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI2">
         <v>0.976</v>
@@ -904,7 +904,7 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -913,7 +913,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -940,31 +940,31 @@
         <v>5</v>
       </c>
       <c r="T3">
-        <v>0.1748</v>
+        <v>0.167</v>
       </c>
       <c r="U3">
-        <v>0.1692</v>
+        <v>0.1563</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="X3">
-        <v>0.1597</v>
+        <v>0.1379</v>
       </c>
       <c r="Y3">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="AB3">
-        <v>0.7366</v>
+        <v>0.731</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -979,10 +979,10 @@
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.2159</v>
+        <v>0.2158</v>
       </c>
       <c r="AH3">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI3">
         <v>0.88</v>
@@ -1017,7 +1017,7 @@
         <v>-110</v>
       </c>
       <c r="F4">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1026,7 +1026,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1041,7 +1041,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1053,31 +1053,31 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>0.1784</v>
+        <v>0.1765</v>
       </c>
       <c r="U4">
-        <v>0.1693</v>
+        <v>0.166</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="X4">
-        <v>0.1538</v>
+        <v>0.1488</v>
       </c>
       <c r="Y4">
-        <v>0.369</v>
+        <v>0.377</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="AB4">
-        <v>0.9488</v>
+        <v>0.9416</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1092,10 +1092,10 @@
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.247</v>
+        <v>0.2468</v>
       </c>
       <c r="AH4">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI4">
         <v>0.9662</v>
@@ -1130,7 +1130,7 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>5.99</v>
+        <v>5.88</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1139,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>5.99</v>
+        <v>5.88</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -1154,7 +1154,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1166,31 +1166,31 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>0.2081</v>
+        <v>0.2094</v>
       </c>
       <c r="U5">
-        <v>0.1908</v>
+        <v>0.1927</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="X5">
-        <v>0.1569</v>
+        <v>0.1556</v>
       </c>
       <c r="Y5">
-        <v>0.338</v>
+        <v>0.31</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="AB5">
-        <v>1.2973</v>
+        <v>1.2874</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1205,10 +1205,10 @@
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2564</v>
+        <v>0.2563</v>
       </c>
       <c r="AH5">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI5">
         <v>1.0729</v>
@@ -1243,7 +1243,7 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>5.02</v>
+        <v>5.21</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1252,7 +1252,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>5.02</v>
+        <v>5.21</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1279,31 +1279,31 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>0.2656</v>
+        <v>0.2702</v>
       </c>
       <c r="U6">
-        <v>0.2479</v>
+        <v>0.259</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="X6">
-        <v>0.215</v>
+        <v>0.2385</v>
       </c>
       <c r="Y6">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="AB6">
-        <v>0.9661</v>
+        <v>0.9588</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1321,7 +1321,7 @@
         <v>0.2096</v>
       </c>
       <c r="AH6">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI6">
         <v>0.8828</v>
@@ -1356,7 +1356,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1365,7 +1365,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1380,7 +1380,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1392,22 +1392,22 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>0.1746</v>
+        <v>0.1792</v>
       </c>
       <c r="U7">
-        <v>0.1764</v>
+        <v>0.1862</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="X7">
-        <v>0.1807</v>
+        <v>0.2</v>
       </c>
       <c r="Y7">
-        <v>0.293</v>
+        <v>0.333</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>4.3</v>
       </c>
       <c r="AB7">
-        <v>1.1248</v>
+        <v>1.1162</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1434,7 +1434,7 @@
         <v>0.2358</v>
       </c>
       <c r="AH7">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI7">
         <v>1.0657</v>
@@ -1469,7 +1469,7 @@
         <v>115</v>
       </c>
       <c r="F8">
-        <v>6.59</v>
+        <v>6.74</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1478,7 +1478,7 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>7.19</v>
+        <v>7.34</v>
       </c>
       <c r="L8" t="s">
         <v>59</v>
@@ -1493,7 +1493,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1505,31 +1505,31 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>0.2641</v>
+        <v>0.2649</v>
       </c>
       <c r="U8">
-        <v>0.254</v>
+        <v>0.2624</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="X8">
-        <v>0.2385</v>
+        <v>0.2583</v>
       </c>
       <c r="Y8">
-        <v>0.394</v>
+        <v>0.375</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="AB8">
-        <v>1.1691</v>
+        <v>1.1601</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>0.2432</v>
       </c>
       <c r="AH8">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI8">
         <v>1.0144</v>
@@ -1582,7 +1582,7 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>6.13</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1591,7 +1591,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>6.13</v>
+        <v>6.02</v>
       </c>
       <c r="L9" t="s">
         <v>62</v>
@@ -1618,31 +1618,31 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>0.2404</v>
+        <v>0.238</v>
       </c>
       <c r="U9">
-        <v>0.2634</v>
+        <v>0.2623</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="X9">
-        <v>0.3176</v>
+        <v>0.3152</v>
       </c>
       <c r="Y9">
-        <v>0.298</v>
+        <v>0.315</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AB9">
-        <v>1.0359</v>
+        <v>1.028</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1660,7 +1660,7 @@
         <v>0.2383</v>
       </c>
       <c r="AH9">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI9">
         <v>1.0083</v>
@@ -1695,7 +1695,7 @@
         <v>103</v>
       </c>
       <c r="F10">
-        <v>6.48</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1704,10 +1704,10 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>6.48</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
@@ -1719,7 +1719,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1731,22 +1731,22 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>0.2851</v>
+        <v>0.2818</v>
       </c>
       <c r="U10">
-        <v>0.3269</v>
+        <v>0.3123</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="X10">
-        <v>0.4037</v>
+        <v>0.3737</v>
       </c>
       <c r="Y10">
-        <v>0.353</v>
+        <v>0.331</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>4.07</v>
       </c>
       <c r="AB10">
-        <v>0.903</v>
+        <v>0.8961</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1773,7 +1773,7 @@
         <v>0.2131</v>
       </c>
       <c r="AH10">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI10">
         <v>0.9582</v>
@@ -1808,7 +1808,7 @@
         <v>-158</v>
       </c>
       <c r="F11">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1817,7 +1817,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
@@ -1832,7 +1832,7 @@
         <v>66</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1844,31 +1844,31 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>0.1677</v>
+        <v>0.1687</v>
       </c>
       <c r="U11">
-        <v>0.1725</v>
+        <v>0.1835</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="X11">
-        <v>0.1828</v>
+        <v>0.2195</v>
       </c>
       <c r="Y11">
-        <v>0.317</v>
+        <v>0.291</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="AB11">
-        <v>0.8937</v>
+        <v>0.8869</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
@@ -1886,7 +1886,7 @@
         <v>0.2175</v>
       </c>
       <c r="AH11">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI11">
         <v>1.0056</v>
@@ -1981,16 +1981,16 @@
         <v>4.21</v>
       </c>
       <c r="AB12">
-        <v>0.9371</v>
+        <v>0.9378</v>
       </c>
       <c r="AC12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.2099</v>
+        <v>0.2116</v>
       </c>
       <c r="AE12">
-        <v>0.2172</v>
+        <v>0.2344</v>
       </c>
       <c r="AF12">
         <v>9</v>
@@ -1999,19 +1999,19 @@
         <v>0.2058</v>
       </c>
       <c r="AH12">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI12">
-        <v>1.0235</v>
+        <v>1.0223</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -2034,7 +2034,7 @@
         <v>-140</v>
       </c>
       <c r="F13">
-        <v>5.61</v>
+        <v>6.63</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2043,10 +2043,10 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>5.61</v>
+        <v>6.63</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M13" t="s">
         <v>68</v>
@@ -2094,16 +2094,16 @@
         <v>4.29</v>
       </c>
       <c r="AB13">
-        <v>1.0039</v>
+        <v>1.1257</v>
       </c>
       <c r="AC13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.2248</v>
+        <v>0.254</v>
       </c>
       <c r="AE13">
-        <v>0.2241</v>
+        <v>0.2457</v>
       </c>
       <c r="AF13">
         <v>9</v>
@@ -2112,19 +2112,19 @@
         <v>0.2169</v>
       </c>
       <c r="AH13">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI13">
-        <v>0.9827</v>
+        <v>1.0367</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2135,7 +2135,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2147,7 +2147,7 @@
         <v>-152</v>
       </c>
       <c r="F14">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2156,13 +2156,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N14">
         <v>823669</v>
@@ -2207,10 +2207,10 @@
         <v>4.35</v>
       </c>
       <c r="AB14">
-        <v>0.8671</v>
+        <v>0.8605</v>
       </c>
       <c r="AC14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD14">
         <v>0.1942</v>
@@ -2225,7 +2225,7 @@
         <v>0.2096</v>
       </c>
       <c r="AH14">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI14">
         <v>0.9817</v>
@@ -2234,10 +2234,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>111</v>
       </c>
       <c r="F15">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2269,13 +2269,13 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N15">
         <v>823669</v>
@@ -2320,10 +2320,10 @@
         <v>4.22</v>
       </c>
       <c r="AB15">
-        <v>0.8192</v>
+        <v>0.8129</v>
       </c>
       <c r="AC15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD15">
         <v>0.1835</v>
@@ -2338,7 +2338,7 @@
         <v>0.2264</v>
       </c>
       <c r="AH15">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI15">
         <v>0.9744</v>
@@ -2347,10 +2347,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>7.45</v>
+        <v>7.38</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2382,7 +2382,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>8.05</v>
+        <v>7.98</v>
       </c>
       <c r="L16" t="s">
         <v>59</v>
@@ -2433,10 +2433,10 @@
         <v>4.1</v>
       </c>
       <c r="AB16">
-        <v>1.2068</v>
+        <v>1.1976</v>
       </c>
       <c r="AC16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD16">
         <v>0.2703</v>
@@ -2451,7 +2451,7 @@
         <v>0.2504</v>
       </c>
       <c r="AH16">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI16">
         <v>1.0463</v>
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM16">
         <v>-0.6</v>
@@ -2477,7 +2477,7 @@
         <v>77</v>
       </c>
       <c r="F17">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2486,7 +2486,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -2537,10 +2537,10 @@
         <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>0.9654</v>
+        <v>0.958</v>
       </c>
       <c r="AC17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD17">
         <v>0.2162</v>
@@ -2555,7 +2555,7 @@
         <v>0.2203</v>
       </c>
       <c r="AH17">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI17">
         <v>1.0271</v>
@@ -2564,10 +2564,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>-120</v>
       </c>
       <c r="F18">
-        <v>6.86</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2599,7 +2599,7 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>6.86</v>
+        <v>6.8</v>
       </c>
       <c r="L18" t="s">
         <v>62</v>
@@ -2650,10 +2650,10 @@
         <v>4.19</v>
       </c>
       <c r="AB18">
-        <v>1.2574</v>
+        <v>1.2478</v>
       </c>
       <c r="AC18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD18">
         <v>0.2816</v>
@@ -2668,7 +2668,7 @@
         <v>0.1991</v>
       </c>
       <c r="AH18">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI18">
         <v>1.0027</v>
@@ -2677,10 +2677,10 @@
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>107</v>
       </c>
       <c r="F19">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2712,7 +2712,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -2763,10 +2763,10 @@
         <v>4.25</v>
       </c>
       <c r="AB19">
-        <v>0.9176</v>
+        <v>0.9106</v>
       </c>
       <c r="AC19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD19">
         <v>0.2055</v>
@@ -2781,7 +2781,7 @@
         <v>0.2145</v>
       </c>
       <c r="AH19">
-        <v>0.224</v>
+        <v>0.2257</v>
       </c>
       <c r="AI19">
         <v>1.0081</v>
@@ -2790,10 +2790,10 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AM19">
         <v>0</v>

--- a/data/k-props/2026-08-13.xlsx
+++ b/data/k-props/2026-08-13.xlsx
@@ -229,19 +229,19 @@
     <t>Philadelphia Phillies @ Minnesota Twins</t>
   </si>
   <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
   </si>
   <si>
     <t>Walbert Ureña</t>
@@ -791,7 +791,7 @@
         <v>-116</v>
       </c>
       <c r="F2">
-        <v>5.57</v>
+        <v>5.66</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -800,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>5.57</v>
+        <v>5.66</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -851,7 +851,7 @@
         <v>3.97</v>
       </c>
       <c r="AB2">
-        <v>0.9428</v>
+        <v>0.9578</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -866,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.2257</v>
+        <v>0.2262</v>
       </c>
       <c r="AH2">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI2">
         <v>0.976</v>
@@ -904,7 +904,7 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -913,7 +913,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -964,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="AB3">
-        <v>0.731</v>
+        <v>0.7426</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -979,10 +979,10 @@
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.2158</v>
+        <v>0.2141</v>
       </c>
       <c r="AH3">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI3">
         <v>0.88</v>
@@ -1017,7 +1017,7 @@
         <v>-110</v>
       </c>
       <c r="F4">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1026,7 +1026,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1077,7 +1077,7 @@
         <v>4.35</v>
       </c>
       <c r="AB4">
-        <v>0.9416</v>
+        <v>0.9565</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1092,10 +1092,10 @@
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.2468</v>
+        <v>0.2448</v>
       </c>
       <c r="AH4">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI4">
         <v>0.9662</v>
@@ -1130,7 +1130,7 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1139,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -1190,7 +1190,7 @@
         <v>4.24</v>
       </c>
       <c r="AB5">
-        <v>1.2874</v>
+        <v>1.3078</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1205,10 +1205,10 @@
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2563</v>
+        <v>0.2548</v>
       </c>
       <c r="AH5">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI5">
         <v>1.0729</v>
@@ -1243,7 +1243,7 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>5.21</v>
+        <v>5.32</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1252,7 +1252,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>5.21</v>
+        <v>5.32</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1267,7 +1267,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1279,22 +1279,22 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>0.2702</v>
+        <v>0.27</v>
       </c>
       <c r="U6">
-        <v>0.259</v>
+        <v>0.2588</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="X6">
-        <v>0.2385</v>
+        <v>0.2389</v>
       </c>
       <c r="Y6">
-        <v>0.353</v>
+        <v>0.361</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1303,7 +1303,7 @@
         <v>4.06</v>
       </c>
       <c r="AB6">
-        <v>0.9588</v>
+        <v>0.974</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1318,10 +1318,10 @@
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2096</v>
+        <v>0.2108</v>
       </c>
       <c r="AH6">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI6">
         <v>0.8828</v>
@@ -1356,7 +1356,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1365,7 +1365,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1416,7 +1416,7 @@
         <v>4.3</v>
       </c>
       <c r="AB7">
-        <v>1.1162</v>
+        <v>1.1339</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1431,10 +1431,10 @@
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>0.2358</v>
+        <v>0.2352</v>
       </c>
       <c r="AH7">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI7">
         <v>1.0657</v>
@@ -1469,7 +1469,7 @@
         <v>115</v>
       </c>
       <c r="F8">
-        <v>6.74</v>
+        <v>7.02</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1478,7 +1478,7 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>7.34</v>
+        <v>7.62</v>
       </c>
       <c r="L8" t="s">
         <v>59</v>
@@ -1493,7 +1493,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1505,22 +1505,22 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>0.2649</v>
+        <v>0.2662</v>
       </c>
       <c r="U8">
-        <v>0.2624</v>
+        <v>0.2678</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X8">
-        <v>0.2583</v>
+        <v>0.2705</v>
       </c>
       <c r="Y8">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>3.93</v>
       </c>
       <c r="AB8">
-        <v>1.1601</v>
+        <v>1.1785</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1544,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.2432</v>
+        <v>0.2442</v>
       </c>
       <c r="AH8">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI8">
         <v>1.0144</v>
@@ -1582,7 +1582,7 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1591,7 +1591,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="L9" t="s">
         <v>62</v>
@@ -1642,7 +1642,7 @@
         <v>3.85</v>
       </c>
       <c r="AB9">
-        <v>1.028</v>
+        <v>1.0443</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1657,10 +1657,10 @@
         <v>9</v>
       </c>
       <c r="AG9">
-        <v>0.2383</v>
+        <v>0.2384</v>
       </c>
       <c r="AH9">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI9">
         <v>1.0083</v>
@@ -1695,7 +1695,7 @@
         <v>103</v>
       </c>
       <c r="F10">
-        <v>5.9</v>
+        <v>6.07</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1704,10 +1704,10 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>6.07</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
@@ -1719,7 +1719,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1731,31 +1731,31 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>0.2818</v>
+        <v>0.2777</v>
       </c>
       <c r="U10">
-        <v>0.3123</v>
+        <v>0.3017</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="X10">
-        <v>0.3737</v>
+        <v>0.3417</v>
       </c>
       <c r="Y10">
-        <v>0.331</v>
+        <v>0.375</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="AB10">
-        <v>0.8961</v>
+        <v>0.9103</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1770,10 +1770,10 @@
         <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.2131</v>
+        <v>0.2119</v>
       </c>
       <c r="AH10">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI10">
         <v>0.9582</v>
@@ -1808,7 +1808,7 @@
         <v>-158</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1817,7 +1817,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
@@ -1832,7 +1832,7 @@
         <v>66</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1844,31 +1844,31 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>0.1687</v>
+        <v>0.1713</v>
       </c>
       <c r="U11">
-        <v>0.1835</v>
+        <v>0.186</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="X11">
-        <v>0.2195</v>
+        <v>0.2165</v>
       </c>
       <c r="Y11">
-        <v>0.291</v>
+        <v>0.327</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.49</v>
+        <v>4.41</v>
       </c>
       <c r="AB11">
-        <v>0.8869</v>
+        <v>0.901</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
@@ -1883,10 +1883,10 @@
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>0.2175</v>
+        <v>0.2165</v>
       </c>
       <c r="AH11">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI11">
         <v>1.0056</v>
@@ -1921,7 +1921,7 @@
         <v>124</v>
       </c>
       <c r="F12">
-        <v>4.88</v>
+        <v>4.97</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1930,7 +1930,7 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>4.88</v>
+        <v>4.97</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
@@ -1957,31 +1957,31 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>0.2314</v>
+        <v>0.2347</v>
       </c>
       <c r="U12">
-        <v>0.2159</v>
+        <v>0.2168</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="X12">
-        <v>0.1901</v>
+        <v>0.1864</v>
       </c>
       <c r="Y12">
-        <v>0.377</v>
+        <v>0.371</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="AB12">
-        <v>0.9378</v>
+        <v>0.9526</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
@@ -1999,7 +1999,7 @@
         <v>0.2058</v>
       </c>
       <c r="AH12">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI12">
         <v>1.0223</v>
@@ -2034,7 +2034,7 @@
         <v>-140</v>
       </c>
       <c r="F13">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2043,7 +2043,7 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="L13" t="s">
         <v>62</v>
@@ -2058,7 +2058,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2070,31 +2070,31 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>0.2554</v>
+        <v>0.2596</v>
       </c>
       <c r="U13">
-        <v>0.2573</v>
+        <v>0.256</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="X13">
-        <v>0.2605</v>
+        <v>0.25</v>
       </c>
       <c r="Y13">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="AB13">
-        <v>1.1257</v>
+        <v>1.1435</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
@@ -2112,7 +2112,7 @@
         <v>0.2169</v>
       </c>
       <c r="AH13">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI13">
         <v>1.0367</v>
@@ -2147,7 +2147,7 @@
         <v>-152</v>
       </c>
       <c r="F14">
-        <v>4.47</v>
+        <v>4.76</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2156,7 +2156,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.47</v>
+        <v>4.76</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -2207,16 +2207,16 @@
         <v>4.35</v>
       </c>
       <c r="AB14">
-        <v>0.8605</v>
+        <v>0.9285</v>
       </c>
       <c r="AC14" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AD14">
-        <v>0.1942</v>
+        <v>0.2063</v>
       </c>
       <c r="AE14">
-        <v>0.1943</v>
+        <v>0.1929</v>
       </c>
       <c r="AF14">
         <v>9</v>
@@ -2225,19 +2225,19 @@
         <v>0.2096</v>
       </c>
       <c r="AH14">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI14">
-        <v>0.9817</v>
+        <v>0.9692</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2260,7 +2260,7 @@
         <v>111</v>
       </c>
       <c r="F15">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2269,7 +2269,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2320,10 +2320,10 @@
         <v>4.22</v>
       </c>
       <c r="AB15">
-        <v>0.8129</v>
+        <v>0.8258</v>
       </c>
       <c r="AC15" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AD15">
         <v>0.1835</v>
@@ -2338,19 +2338,19 @@
         <v>0.2264</v>
       </c>
       <c r="AH15">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI15">
-        <v>0.9744</v>
+        <v>0.9489</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>6.5</v>
@@ -2373,7 +2373,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2382,13 +2382,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>7.98</v>
+        <v>8.11</v>
       </c>
       <c r="L16" t="s">
         <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N16">
         <v>823995</v>
@@ -2433,10 +2433,10 @@
         <v>4.1</v>
       </c>
       <c r="AB16">
-        <v>1.1976</v>
+        <v>1.2166</v>
       </c>
       <c r="AC16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AD16">
         <v>0.2703</v>
@@ -2451,7 +2451,7 @@
         <v>0.2504</v>
       </c>
       <c r="AH16">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI16">
         <v>1.0463</v>
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AM16">
         <v>-0.6</v>
@@ -2477,7 +2477,7 @@
         <v>77</v>
       </c>
       <c r="F17">
-        <v>4.94</v>
+        <v>5.02</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2486,13 +2486,13 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>4.94</v>
+        <v>5.02</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N17">
         <v>823995</v>
@@ -2537,10 +2537,10 @@
         <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>0.958</v>
+        <v>0.9732</v>
       </c>
       <c r="AC17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AD17">
         <v>0.2162</v>
@@ -2555,7 +2555,7 @@
         <v>0.2203</v>
       </c>
       <c r="AH17">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI17">
         <v>1.0271</v>
@@ -2564,10 +2564,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>-120</v>
       </c>
       <c r="F18">
-        <v>6.8</v>
+        <v>5.05</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2599,10 +2599,10 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>6.8</v>
+        <v>5.05</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
@@ -2650,16 +2650,16 @@
         <v>4.19</v>
       </c>
       <c r="AB18">
-        <v>1.2478</v>
+        <v>0.928</v>
       </c>
       <c r="AC18" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AD18">
-        <v>0.2816</v>
+        <v>0.2062</v>
       </c>
       <c r="AE18">
-        <v>0.2193</v>
+        <v>0.1981</v>
       </c>
       <c r="AF18">
         <v>9</v>
@@ -2668,19 +2668,19 @@
         <v>0.1991</v>
       </c>
       <c r="AH18">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI18">
-        <v>1.0027</v>
+        <v>1.0015</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>107</v>
       </c>
       <c r="F19">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2712,7 +2712,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -2763,10 +2763,10 @@
         <v>4.25</v>
       </c>
       <c r="AB19">
-        <v>0.9106</v>
+        <v>0.925</v>
       </c>
       <c r="AC19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AD19">
         <v>0.2055</v>
@@ -2781,7 +2781,7 @@
         <v>0.2145</v>
       </c>
       <c r="AH19">
-        <v>0.2257</v>
+        <v>0.2222</v>
       </c>
       <c r="AI19">
         <v>1.0081</v>
@@ -2790,10 +2790,10 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2825,7 +2825,7 @@
         <v>45</v>
       </c>
       <c r="M20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
         <v>45</v>
